--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_6902.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_6902.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R29"/>
+  <dimension ref="A1:S29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +509,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1722,6 +1727,12 @@
           <t>6902-04-04-NWO-FG</t>
         </is>
       </c>
+      <c r="F21" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.6879999999999999</v>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>6902-04-04-NWO-FG</t>
@@ -1734,12 +1745,12 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6902-04-04 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, C1HEX@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6902-04-04 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6902-04-04 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6902-04-04 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6902-04-04-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, C1HEX@HEX=C1; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -1750,6 +1761,11 @@
       <c r="R21" t="inlineStr">
         <is>
           <t>6902-04-04-NWO-FG</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1759,6 +1775,9 @@
           <t>6902-06-04-NWO-FG</t>
         </is>
       </c>
+      <c r="F22" t="n">
+        <v>0.6879999999999999</v>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>6902-06-04-NWO-FG</t>
@@ -1771,12 +1790,12 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6902-06-04 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6902-06-04 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6902-06-04 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6902-06-04 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6902-06-04-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -1787,6 +1806,11 @@
       <c r="R22" t="inlineStr">
         <is>
           <t>6902-06-04-NWO-FG</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1796,6 +1820,12 @@
           <t>6902-06-06-NWO-FG</t>
         </is>
       </c>
+      <c r="F23" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.875</v>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>6902-06-06-NWO-FG</t>
@@ -1808,12 +1838,12 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6902-06-06 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, C1HEX@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6902-06-06 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6902-06-06 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6902-06-06 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6902-06-06-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, C1HEX@HEX=C1; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -1824,6 +1854,11 @@
       <c r="R23" t="inlineStr">
         <is>
           <t>6902-06-06-NWO-FG</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1833,6 +1868,12 @@
           <t>6902-08-06-NWO-FG</t>
         </is>
       </c>
+      <c r="F24" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.875</v>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>6902-08-06-NWO-FG</t>
@@ -1845,12 +1886,12 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6902-08-06 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, C1HEX@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6902-08-06 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6902-08-06 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6902-08-06 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6902-08-06-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, C1HEX@HEX=C1; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -1861,6 +1902,11 @@
       <c r="R24" t="inlineStr">
         <is>
           <t>6902-08-06-NWO-FG</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1870,6 +1916,12 @@
           <t>6902-08-08-NWO-FG</t>
         </is>
       </c>
+      <c r="F25" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>6902-08-08-NWO-FG</t>
@@ -1882,12 +1934,12 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6902-08-08 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, C1HEX@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6902-08-08 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6902-08-08 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6902-08-08 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6902-08-08-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, C1HEX@HEX=C1; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -1898,6 +1950,11 @@
       <c r="R25" t="inlineStr">
         <is>
           <t>6902-08-08-NWO-FG</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1907,6 +1964,12 @@
           <t>6902-10-08-NWO-FG</t>
         </is>
       </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>6902-10-08-NWO-FG</t>
@@ -1919,12 +1982,12 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6902-10-08 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, C1HEX@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6902-10-08 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6902-10-08 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6902-10-08 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6902-10-08-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, C1HEX@HEX=C1; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -1935,6 +1998,11 @@
       <c r="R26" t="inlineStr">
         <is>
           <t>6902-10-08-NWO-FG</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1944,6 +2012,12 @@
           <t>6902-10-12-NWO-FG</t>
         </is>
       </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.25</v>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>6902-10-12-NWO-FG</t>
@@ -1956,12 +2030,12 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6902-10-12 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, C1HEX@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6902-10-12 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6902-10-12 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6902-10-12 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6902-10-12-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, C1HEX@HEX=C1; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -1972,6 +2046,11 @@
       <c r="R27" t="inlineStr">
         <is>
           <t>6902-10-12-NWO-FG</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1981,6 +2060,12 @@
           <t>6902-16-16-NWO-FG</t>
         </is>
       </c>
+      <c r="F28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.5</v>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>6902-16-16-NWO-FG</t>
@@ -1993,12 +2078,12 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6902-16-16 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, C1HEX@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6902-16-16 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6902-16-16 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6902-16-16 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6902-16-16-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, C1HEX@HEX=C1; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2009,6 +2094,11 @@
       <c r="R28" t="inlineStr">
         <is>
           <t>6902-16-16-NWO-FG</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -2018,6 +2108,12 @@
           <t>6902-24-24-NWO-FG</t>
         </is>
       </c>
+      <c r="F29" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2.125</v>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>6902-24-24-NWO-FG</t>
@@ -2030,12 +2126,12 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, C1HEX@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | Brennan CAD record 6902-24-24-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, C1HEX@HEX=C1; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -2046,6 +2142,11 @@
       <c r="R29" t="inlineStr">
         <is>
           <t>6902-24-24-NWO-FG</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>

--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_6902.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_6902.xlsx
@@ -1727,12 +1727,24 @@
           <t>6902-04-04-NWO-FG</t>
         </is>
       </c>
+      <c r="E21" t="n">
+        <v>0.6879999999999999</v>
+      </c>
       <c r="F21" t="n">
         <v>0.5629999999999999</v>
       </c>
       <c r="G21" t="n">
         <v>0.6879999999999999</v>
       </c>
+      <c r="H21" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.4375</v>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>6902-04-04-NWO-FG</t>
@@ -1745,12 +1757,12 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, C1HEX@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6902-04-04 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, C1HEX@HEX, CHEX@HEX, D1@BORE, D@BORE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6902-04-04 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6902-04-04 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6902-04-04-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, C1HEX@HEX=C1; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6902-04-04 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6902-04-04-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, C1HEX@HEX=C1, CHEX@HEX=C1, D1@BORE=BD, D@BORE=AD, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -1775,9 +1787,21 @@
           <t>6902-06-04-NWO-FG</t>
         </is>
       </c>
+      <c r="E22" t="n">
+        <v>0.6879999999999999</v>
+      </c>
       <c r="F22" t="n">
         <v>0.6879999999999999</v>
       </c>
+      <c r="H22" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.5625</v>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>6902-06-04-NWO-FG</t>
@@ -1790,12 +1814,12 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6902-06-04 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, CHEX@HEX, D1@BORE, D@BORE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6902-06-04 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6902-06-04 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6902-06-04-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6902-06-04 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6902-06-04-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, CHEX@HEX=C1, D1@BORE=BD, D@BORE=AD, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -1820,12 +1844,24 @@
           <t>6902-06-06-NWO-FG</t>
         </is>
       </c>
+      <c r="E23" t="n">
+        <v>0.875</v>
+      </c>
       <c r="F23" t="n">
         <v>0.6879999999999999</v>
       </c>
       <c r="G23" t="n">
         <v>0.875</v>
       </c>
+      <c r="H23" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.5625</v>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>6902-06-06-NWO-FG</t>
@@ -1838,12 +1874,12 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, C1HEX@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6902-06-06 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, C1HEX@HEX, CHEX@HEX, D1@BORE, D@BORE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6902-06-06 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6902-06-06 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6902-06-06-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, C1HEX@HEX=C1; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6902-06-06 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6902-06-06-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, C1HEX@HEX=C1, CHEX@HEX=C1, D1@BORE=BD, D@BORE=AD, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -1868,12 +1904,24 @@
           <t>6902-08-06-NWO-FG</t>
         </is>
       </c>
+      <c r="E24" t="n">
+        <v>0.875</v>
+      </c>
       <c r="F24" t="n">
         <v>0.875</v>
       </c>
       <c r="G24" t="n">
         <v>0.875</v>
       </c>
+      <c r="H24" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.75</v>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>6902-08-06-NWO-FG</t>
@@ -1886,12 +1934,12 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, C1HEX@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6902-08-06 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, C1HEX@HEX, CHEX@HEX, D1@BORE, D@BORE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6902-08-06 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6902-08-06 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6902-08-06-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, C1HEX@HEX=C1; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6902-08-06 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6902-08-06-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, C1HEX@HEX=C1, CHEX@HEX=C1, D1@BORE=BD, D@BORE=AD, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -1916,12 +1964,24 @@
           <t>6902-08-08-NWO-FG</t>
         </is>
       </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
       <c r="F25" t="n">
         <v>0.875</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
+      <c r="H25" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.75</v>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>6902-08-08-NWO-FG</t>
@@ -1934,12 +1994,12 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, C1HEX@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6902-08-08 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, C1HEX@HEX, CHEX@HEX, D1@BORE, D@BORE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6902-08-08 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6902-08-08 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6902-08-08-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, C1HEX@HEX=C1; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6902-08-08 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6902-08-08-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, C1HEX@HEX=C1, CHEX@HEX=C1, D1@BORE=BD, D@BORE=AD, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -1964,12 +2024,24 @@
           <t>6902-10-08-NWO-FG</t>
         </is>
       </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
+      <c r="H26" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.875</v>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>6902-10-08-NWO-FG</t>
@@ -1982,12 +2054,12 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, C1HEX@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6902-10-08 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, C1HEX@HEX, CHEX@HEX, D1@BORE, D@BORE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6902-10-08 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6902-10-08 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6902-10-08-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, C1HEX@HEX=C1; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6902-10-08 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6902-10-08-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, C1HEX@HEX=C1, CHEX@HEX=C1, D1@BORE=BD, D@BORE=AD, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2012,12 +2084,24 @@
           <t>6902-10-12-NWO-FG</t>
         </is>
       </c>
+      <c r="E27" t="n">
+        <v>1.25</v>
+      </c>
       <c r="F27" t="n">
         <v>1</v>
       </c>
       <c r="G27" t="n">
         <v>1.25</v>
       </c>
+      <c r="H27" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.875</v>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>6902-10-12-NWO-FG</t>
@@ -2030,12 +2114,12 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, C1HEX@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6902-10-12 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, C1HEX@HEX, CHEX@HEX, D1@BORE, D@BORE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6902-10-12 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6902-10-12 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6902-10-12-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, C1HEX@HEX=C1; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6902-10-12 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6902-10-12-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, C1HEX@HEX=C1, CHEX@HEX=C1, D1@BORE=BD, D@BORE=AD, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -2060,12 +2144,24 @@
           <t>6902-16-16-NWO-FG</t>
         </is>
       </c>
+      <c r="E28" t="n">
+        <v>1.5</v>
+      </c>
       <c r="F28" t="n">
         <v>1.5</v>
       </c>
       <c r="G28" t="n">
         <v>1.5</v>
       </c>
+      <c r="H28" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.3125</v>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>6902-16-16-NWO-FG</t>
@@ -2078,12 +2174,12 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, C1HEX@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6902-16-16 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, C1HEX@HEX, CHEX@HEX, D1@BORE, D@BORE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6902-16-16 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6902-16-16 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6902-16-16-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, C1HEX@HEX=C1; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6902-16-16 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6902-16-16-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, C1HEX@HEX=C1, CHEX@HEX=C1, D1@BORE=BD, D@BORE=AD, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2108,12 +2204,24 @@
           <t>6902-24-24-NWO-FG</t>
         </is>
       </c>
+      <c r="E29" t="n">
+        <v>2.125</v>
+      </c>
       <c r="F29" t="n">
         <v>2.125</v>
       </c>
       <c r="G29" t="n">
         <v>2.125</v>
       </c>
+      <c r="H29" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.875</v>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>6902-24-24-NWO-FG</t>
@@ -2126,12 +2234,12 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, C1HEX@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, C1HEX@HEX, CHEX@HEX, D1@BORE, D@BORE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | Brennan CAD record 6902-24-24-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, C1HEX@HEX=C1; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | Brennan CAD record 6902-24-24-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, C1HEX@HEX=C1, CHEX@HEX=C1, D1@BORE=BD, D@BORE=AD, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
